--- a/docs/เทียบทุน-ก่อนหลัง-ราคาอลู3แบรนด์.xlsx
+++ b/docs/เทียบทุน-ก่อนหลัง-ราคาอลู3แบรนด์.xlsx
@@ -214,7 +214,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -223,22 +223,22 @@
         </is>
       </c>
       <c r="D4">
-        <v>25438</v>
+        <v>4302</v>
       </c>
       <c r="E4">
-        <v>30379</v>
+        <v>5574</v>
       </c>
       <c r="F4">
-        <v>4941</v>
+        <v>1272</v>
       </c>
       <c r="G4">
-        <v>19.4</v>
+        <v>29.6</v>
       </c>
       <c r="H4">
-        <v>13860</v>
+        <v>3240</v>
       </c>
       <c r="I4">
-        <v>18801</v>
+        <v>4512</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -250,7 +250,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -259,22 +259,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>4302</v>
+        <v>25438</v>
       </c>
       <c r="E5">
-        <v>5058</v>
+        <v>30379</v>
       </c>
       <c r="F5">
-        <v>756</v>
+        <v>4941</v>
       </c>
       <c r="G5">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
       <c r="H5">
-        <v>3240</v>
+        <v>13860</v>
       </c>
       <c r="I5">
-        <v>3996</v>
+        <v>18801</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -610,31 +610,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D15">
-        <v>18301</v>
+        <v>4302</v>
       </c>
       <c r="E15">
-        <v>20135</v>
+        <v>4792</v>
       </c>
       <c r="F15">
-        <v>1833</v>
+        <v>490</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="H15">
-        <v>10098</v>
+        <v>3240</v>
       </c>
       <c r="I15">
-        <v>11931</v>
+        <v>3730</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -646,31 +646,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D16">
-        <v>18301</v>
+        <v>18014</v>
       </c>
       <c r="E16">
-        <v>20135</v>
+        <v>15956</v>
       </c>
       <c r="F16">
-        <v>1833</v>
+        <v>-2058</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>-11.4</v>
       </c>
       <c r="H16">
-        <v>10098</v>
+        <v>14506</v>
       </c>
       <c r="I16">
-        <v>11931</v>
+        <v>12448</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -687,26 +687,26 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D17">
-        <v>19199</v>
+        <v>18301</v>
       </c>
       <c r="E17">
-        <v>21088</v>
+        <v>20135</v>
       </c>
       <c r="F17">
-        <v>1889</v>
+        <v>1833</v>
       </c>
       <c r="G17">
-        <v>9.8</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>10995</v>
+        <v>10098</v>
       </c>
       <c r="I17">
-        <v>12884</v>
+        <v>11931</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -718,31 +718,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D18">
-        <v>18014</v>
+        <v>18301</v>
       </c>
       <c r="E18">
-        <v>16404</v>
+        <v>20135</v>
       </c>
       <c r="F18">
-        <v>-1610</v>
+        <v>1833</v>
       </c>
       <c r="G18">
-        <v>-8.9</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>14506</v>
+        <v>10098</v>
       </c>
       <c r="I18">
-        <v>12896</v>
+        <v>11931</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -754,31 +754,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D19">
-        <v>19474</v>
+        <v>19199</v>
       </c>
       <c r="E19">
-        <v>17864</v>
+        <v>21088</v>
       </c>
       <c r="F19">
-        <v>-1610</v>
+        <v>1889</v>
       </c>
       <c r="G19">
-        <v>-8.3</v>
+        <v>9.8</v>
       </c>
       <c r="H19">
-        <v>15966</v>
+        <v>10995</v>
       </c>
       <c r="I19">
-        <v>14356</v>
+        <v>12884</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -790,7 +790,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">awning</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -799,22 +799,22 @@
         </is>
       </c>
       <c r="D20">
-        <v>2665</v>
+        <v>19474</v>
       </c>
       <c r="E20">
-        <v>2491</v>
+        <v>17864</v>
       </c>
       <c r="F20">
-        <v>-174</v>
+        <v>-1610</v>
       </c>
       <c r="G20">
-        <v>-6.5</v>
+        <v>-8.3</v>
       </c>
       <c r="H20">
-        <v>1494</v>
+        <v>15966</v>
       </c>
       <c r="I20">
-        <v>1320</v>
+        <v>14356</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -826,7 +826,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,22 +835,22 @@
         </is>
       </c>
       <c r="D21">
-        <v>18014</v>
+        <v>4302</v>
       </c>
       <c r="E21">
-        <v>16837</v>
+        <v>4654</v>
       </c>
       <c r="F21">
-        <v>-1177</v>
+        <v>352</v>
       </c>
       <c r="G21">
-        <v>-6.5</v>
+        <v>8.2</v>
       </c>
       <c r="H21">
-        <v>14506</v>
+        <v>3240</v>
       </c>
       <c r="I21">
-        <v>13329</v>
+        <v>3592</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -867,26 +867,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D22">
         <v>18014</v>
       </c>
       <c r="E22">
-        <v>16837</v>
+        <v>16549</v>
       </c>
       <c r="F22">
-        <v>-1177</v>
+        <v>-1465</v>
       </c>
       <c r="G22">
-        <v>-6.5</v>
+        <v>-8.1</v>
       </c>
       <c r="H22">
         <v>14506</v>
       </c>
       <c r="I22">
-        <v>13329</v>
+        <v>13041</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -898,31 +898,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D23">
-        <v>18524</v>
+        <v>18014</v>
       </c>
       <c r="E23">
-        <v>19699</v>
+        <v>16549</v>
       </c>
       <c r="F23">
-        <v>1176</v>
+        <v>-1465</v>
       </c>
       <c r="G23">
-        <v>6.3</v>
+        <v>-8.1</v>
       </c>
       <c r="H23">
-        <v>12045</v>
+        <v>14506</v>
       </c>
       <c r="I23">
-        <v>13221</v>
+        <v>13041</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -934,31 +934,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide</t>
+          <t xml:space="preserve">awning</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D24">
-        <v>18524</v>
+        <v>2665</v>
       </c>
       <c r="E24">
-        <v>19699</v>
+        <v>2491</v>
       </c>
       <c r="F24">
-        <v>1176</v>
+        <v>-174</v>
       </c>
       <c r="G24">
-        <v>6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="H24">
-        <v>12045</v>
+        <v>1494</v>
       </c>
       <c r="I24">
-        <v>13221</v>
+        <v>1320</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -970,7 +970,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">sms_slide</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -979,22 +979,22 @@
         </is>
       </c>
       <c r="D25">
-        <v>4302</v>
+        <v>18524</v>
       </c>
       <c r="E25">
-        <v>4036</v>
+        <v>19699</v>
       </c>
       <c r="F25">
-        <v>-266</v>
+        <v>1176</v>
       </c>
       <c r="G25">
-        <v>-6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H25">
-        <v>3240</v>
+        <v>12045</v>
       </c>
       <c r="I25">
-        <v>2974</v>
+        <v>13221</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1006,7 +1006,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">sms_slide</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D26">
-        <v>4302</v>
+        <v>18524</v>
       </c>
       <c r="E26">
-        <v>4036</v>
+        <v>19699</v>
       </c>
       <c r="F26">
-        <v>-266</v>
+        <v>1176</v>
       </c>
       <c r="G26">
-        <v>-6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H26">
-        <v>3240</v>
+        <v>12045</v>
       </c>
       <c r="I26">
-        <v>2974</v>
+        <v>13221</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1078,7 +1078,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1087,22 +1087,22 @@
         </is>
       </c>
       <c r="D28">
-        <v>18039</v>
+        <v>4302</v>
       </c>
       <c r="E28">
-        <v>17140</v>
+        <v>4552</v>
       </c>
       <c r="F28">
-        <v>-899</v>
+        <v>250</v>
       </c>
       <c r="G28">
-        <v>-5</v>
+        <v>5.8</v>
       </c>
       <c r="H28">
-        <v>15965</v>
+        <v>3240</v>
       </c>
       <c r="I28">
-        <v>15066</v>
+        <v>3490</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1114,31 +1114,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D29">
-        <v>10519</v>
+        <v>18532</v>
       </c>
       <c r="E29">
-        <v>10016</v>
+        <v>19525</v>
       </c>
       <c r="F29">
-        <v>-503</v>
+        <v>993</v>
       </c>
       <c r="G29">
-        <v>-4.8</v>
+        <v>5.4</v>
       </c>
       <c r="H29">
-        <v>5133</v>
+        <v>7449</v>
       </c>
       <c r="I29">
-        <v>4630</v>
+        <v>8442</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1150,31 +1150,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D30">
-        <v>11060</v>
+        <v>18039</v>
       </c>
       <c r="E30">
-        <v>10539</v>
+        <v>17140</v>
       </c>
       <c r="F30">
-        <v>-521</v>
+        <v>-899</v>
       </c>
       <c r="G30">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="H30">
-        <v>5674</v>
+        <v>15965</v>
       </c>
       <c r="I30">
-        <v>5153</v>
+        <v>15066</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1186,31 +1186,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D31">
-        <v>25189</v>
+        <v>10519</v>
       </c>
       <c r="E31">
-        <v>26357</v>
+        <v>10016</v>
       </c>
       <c r="F31">
-        <v>1169</v>
+        <v>-503</v>
       </c>
       <c r="G31">
-        <v>4.6</v>
+        <v>-4.8</v>
       </c>
       <c r="H31">
-        <v>16985</v>
+        <v>5133</v>
       </c>
       <c r="I31">
-        <v>18154</v>
+        <v>4630</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1222,7 +1222,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">bar_slide</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1231,22 +1231,22 @@
         </is>
       </c>
       <c r="D32">
-        <v>18182</v>
+        <v>11060</v>
       </c>
       <c r="E32">
-        <v>18980</v>
+        <v>10539</v>
       </c>
       <c r="F32">
-        <v>798</v>
+        <v>-521</v>
       </c>
       <c r="G32">
-        <v>4.4</v>
+        <v>-4.7</v>
       </c>
       <c r="H32">
-        <v>9959</v>
+        <v>5674</v>
       </c>
       <c r="I32">
-        <v>10757</v>
+        <v>5153</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1258,31 +1258,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D33">
-        <v>18039</v>
+        <v>25189</v>
       </c>
       <c r="E33">
-        <v>17278</v>
+        <v>26357</v>
       </c>
       <c r="F33">
-        <v>-761</v>
+        <v>1169</v>
       </c>
       <c r="G33">
-        <v>-4.2</v>
+        <v>4.6</v>
       </c>
       <c r="H33">
-        <v>15965</v>
+        <v>16985</v>
       </c>
       <c r="I33">
-        <v>15204</v>
+        <v>18154</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1294,31 +1294,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">bar_slide</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D34">
-        <v>14700</v>
+        <v>16989</v>
       </c>
       <c r="E34">
-        <v>15294</v>
+        <v>17779</v>
       </c>
       <c r="F34">
-        <v>594</v>
+        <v>790</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="H34">
-        <v>6477</v>
+        <v>5906</v>
       </c>
       <c r="I34">
-        <v>7071</v>
+        <v>6696</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1330,7 +1330,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">bar_slide</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="D35">
-        <v>14700</v>
+        <v>16727</v>
       </c>
       <c r="E35">
-        <v>15294</v>
+        <v>17467</v>
       </c>
       <c r="F35">
-        <v>594</v>
+        <v>739</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H35">
-        <v>6477</v>
+        <v>5644</v>
       </c>
       <c r="I35">
-        <v>7071</v>
+        <v>6383</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1371,26 +1371,26 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D36">
-        <v>15261</v>
+        <v>18182</v>
       </c>
       <c r="E36">
-        <v>15857</v>
+        <v>18980</v>
       </c>
       <c r="F36">
-        <v>596</v>
+        <v>798</v>
       </c>
       <c r="G36">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="H36">
-        <v>7038</v>
+        <v>9959</v>
       </c>
       <c r="I36">
-        <v>7634</v>
+        <v>10757</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1402,31 +1402,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D37">
-        <v>21140</v>
+        <v>16727</v>
       </c>
       <c r="E37">
-        <v>20343</v>
+        <v>17451</v>
       </c>
       <c r="F37">
-        <v>-797</v>
+        <v>724</v>
       </c>
       <c r="G37">
-        <v>-3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H37">
-        <v>17375</v>
+        <v>5644</v>
       </c>
       <c r="I37">
-        <v>16578</v>
+        <v>6368</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1438,31 +1438,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D38">
-        <v>22100</v>
+        <v>18039</v>
       </c>
       <c r="E38">
-        <v>21269</v>
+        <v>17278</v>
       </c>
       <c r="F38">
-        <v>-831</v>
+        <v>-761</v>
       </c>
       <c r="G38">
-        <v>-3.8</v>
+        <v>-4.2</v>
       </c>
       <c r="H38">
-        <v>9023</v>
+        <v>15965</v>
       </c>
       <c r="I38">
-        <v>8193</v>
+        <v>15204</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1474,31 +1474,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">bar_slide</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D39">
-        <v>22100</v>
+        <v>14700</v>
       </c>
       <c r="E39">
-        <v>21308</v>
+        <v>15294</v>
       </c>
       <c r="F39">
-        <v>-792</v>
+        <v>594</v>
       </c>
       <c r="G39">
-        <v>-3.6</v>
+        <v>4</v>
       </c>
       <c r="H39">
-        <v>9023</v>
+        <v>6477</v>
       </c>
       <c r="I39">
-        <v>8232</v>
+        <v>7071</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1510,31 +1510,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">bar_slide</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D40">
-        <v>20035</v>
+        <v>14700</v>
       </c>
       <c r="E40">
-        <v>19377</v>
+        <v>15294</v>
       </c>
       <c r="F40">
-        <v>-658</v>
+        <v>594</v>
       </c>
       <c r="G40">
-        <v>-3.3</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>16270</v>
+        <v>6477</v>
       </c>
       <c r="I40">
-        <v>15612</v>
+        <v>7071</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -1546,31 +1546,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">bar_slide</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D41">
-        <v>20035</v>
+        <v>15261</v>
       </c>
       <c r="E41">
-        <v>19377</v>
+        <v>15857</v>
       </c>
       <c r="F41">
-        <v>-658</v>
+        <v>596</v>
       </c>
       <c r="G41">
-        <v>-3.3</v>
+        <v>3.9</v>
       </c>
       <c r="H41">
-        <v>16270</v>
+        <v>7038</v>
       </c>
       <c r="I41">
-        <v>15612</v>
+        <v>7634</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -1587,26 +1587,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D42">
-        <v>27485</v>
+        <v>21140</v>
       </c>
       <c r="E42">
-        <v>26572</v>
+        <v>20343</v>
       </c>
       <c r="F42">
-        <v>-913</v>
+        <v>-797</v>
       </c>
       <c r="G42">
-        <v>-3.3</v>
+        <v>-3.8</v>
       </c>
       <c r="H42">
-        <v>23720</v>
+        <v>17375</v>
       </c>
       <c r="I42">
-        <v>22807</v>
+        <v>16578</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -1618,31 +1618,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D43">
-        <v>10519</v>
+        <v>22100</v>
       </c>
       <c r="E43">
-        <v>10186</v>
+        <v>21269</v>
       </c>
       <c r="F43">
-        <v>-333</v>
+        <v>-831</v>
       </c>
       <c r="G43">
-        <v>-3.2</v>
+        <v>-3.8</v>
       </c>
       <c r="H43">
-        <v>5133</v>
+        <v>9023</v>
       </c>
       <c r="I43">
-        <v>4800</v>
+        <v>8193</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -1654,7 +1654,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1663,22 +1663,22 @@
         </is>
       </c>
       <c r="D44">
-        <v>16727</v>
+        <v>22100</v>
       </c>
       <c r="E44">
-        <v>17239</v>
+        <v>21308</v>
       </c>
       <c r="F44">
-        <v>512</v>
+        <v>-792</v>
       </c>
       <c r="G44">
-        <v>3.1</v>
+        <v>-3.6</v>
       </c>
       <c r="H44">
-        <v>5644</v>
+        <v>9023</v>
       </c>
       <c r="I44">
-        <v>6156</v>
+        <v>8232</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -1690,31 +1690,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D45">
-        <v>16989</v>
+        <v>20035</v>
       </c>
       <c r="E45">
-        <v>17509</v>
+        <v>19377</v>
       </c>
       <c r="F45">
-        <v>520</v>
+        <v>-658</v>
       </c>
       <c r="G45">
-        <v>3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H45">
-        <v>5906</v>
+        <v>16270</v>
       </c>
       <c r="I45">
-        <v>6426</v>
+        <v>15612</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -1726,31 +1726,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D46">
-        <v>10597</v>
+        <v>20035</v>
       </c>
       <c r="E46">
-        <v>10266</v>
+        <v>19377</v>
       </c>
       <c r="F46">
-        <v>-331</v>
+        <v>-658</v>
       </c>
       <c r="G46">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="H46">
-        <v>5211</v>
+        <v>16270</v>
       </c>
       <c r="I46">
-        <v>4880</v>
+        <v>15612</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -1762,31 +1762,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D47">
-        <v>4302</v>
+        <v>27485</v>
       </c>
       <c r="E47">
-        <v>4174</v>
+        <v>26572</v>
       </c>
       <c r="F47">
-        <v>-128</v>
+        <v>-913</v>
       </c>
       <c r="G47">
-        <v>-3</v>
+        <v>-3.3</v>
       </c>
       <c r="H47">
-        <v>3240</v>
+        <v>23720</v>
       </c>
       <c r="I47">
-        <v>3112</v>
+        <v>22807</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -1798,31 +1798,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D48">
-        <v>16727</v>
+        <v>10519</v>
       </c>
       <c r="E48">
-        <v>17224</v>
+        <v>10186</v>
       </c>
       <c r="F48">
-        <v>496</v>
+        <v>-333</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>-3.2</v>
       </c>
       <c r="H48">
-        <v>5644</v>
+        <v>5133</v>
       </c>
       <c r="I48">
-        <v>6140</v>
+        <v>4800</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -1834,31 +1834,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">sms_slide</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D49">
-        <v>25650</v>
+        <v>10597</v>
       </c>
       <c r="E49">
-        <v>26396</v>
+        <v>10266</v>
       </c>
       <c r="F49">
-        <v>746</v>
+        <v>-331</v>
       </c>
       <c r="G49">
-        <v>2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="H49">
-        <v>19171</v>
+        <v>5211</v>
       </c>
       <c r="I49">
-        <v>19917</v>
+        <v>4880</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -1870,7 +1870,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">sms_slide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1879,22 +1879,22 @@
         </is>
       </c>
       <c r="D50">
-        <v>18532</v>
+        <v>25650</v>
       </c>
       <c r="E50">
-        <v>18990</v>
+        <v>26396</v>
       </c>
       <c r="F50">
-        <v>458</v>
+        <v>746</v>
       </c>
       <c r="G50">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="H50">
-        <v>7449</v>
+        <v>19171</v>
       </c>
       <c r="I50">
-        <v>7907</v>
+        <v>19917</v>
       </c>
       <c r="J50">
         <v>0</v>

--- a/docs/เทียบทุน-ก่อนหลัง-ราคาอลู3แบรนด์.xlsx
+++ b/docs/เทียบทุน-ก่อนหลัง-ราคาอลู3แบรนด์.xlsx
@@ -250,7 +250,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -259,22 +259,22 @@
         </is>
       </c>
       <c r="D5">
-        <v>25438</v>
+        <v>22100</v>
       </c>
       <c r="E5">
-        <v>30379</v>
+        <v>26896</v>
       </c>
       <c r="F5">
-        <v>4941</v>
+        <v>4796</v>
       </c>
       <c r="G5">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="H5">
-        <v>13860</v>
+        <v>9023</v>
       </c>
       <c r="I5">
-        <v>18801</v>
+        <v>13820</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -286,31 +286,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">banyok</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D6">
-        <v>5252</v>
+        <v>25438</v>
       </c>
       <c r="E6">
-        <v>6087</v>
+        <v>30379</v>
       </c>
       <c r="F6">
-        <v>834</v>
+        <v>4941</v>
       </c>
       <c r="G6">
-        <v>15.9</v>
+        <v>19.4</v>
       </c>
       <c r="H6">
-        <v>2286</v>
+        <v>13860</v>
       </c>
       <c r="I6">
-        <v>3121</v>
+        <v>18801</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -322,7 +322,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">banyok</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -331,22 +331,22 @@
         </is>
       </c>
       <c r="D7">
-        <v>21379</v>
+        <v>5252</v>
       </c>
       <c r="E7">
-        <v>18112</v>
+        <v>6087</v>
       </c>
       <c r="F7">
-        <v>-3267</v>
+        <v>834</v>
       </c>
       <c r="G7">
-        <v>-15.3</v>
+        <v>15.9</v>
       </c>
       <c r="H7">
-        <v>19305</v>
+        <v>2286</v>
       </c>
       <c r="I7">
-        <v>16038</v>
+        <v>3121</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -358,7 +358,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -367,34 +367,34 @@
         </is>
       </c>
       <c r="D8">
-        <v>15355</v>
+        <v>21379</v>
       </c>
       <c r="E8">
-        <v>13308</v>
+        <v>18112</v>
       </c>
       <c r="F8">
-        <v>-2046</v>
+        <v>-3267</v>
       </c>
       <c r="G8">
-        <v>-13.3</v>
+        <v>-15.3</v>
       </c>
       <c r="H8">
-        <v>7465</v>
+        <v>19305</v>
       </c>
       <c r="I8">
-        <v>6997</v>
+        <v>16038</v>
       </c>
       <c r="J8">
-        <v>2089</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">banyok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -403,25 +403,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>14705</v>
+        <v>5252</v>
       </c>
       <c r="E9">
-        <v>12797</v>
+        <v>5871</v>
       </c>
       <c r="F9">
-        <v>-1907</v>
+        <v>619</v>
       </c>
       <c r="G9">
-        <v>-13</v>
+        <v>11.8</v>
       </c>
       <c r="H9">
-        <v>7465</v>
+        <v>2286</v>
       </c>
       <c r="I9">
-        <v>6997</v>
+        <v>2905</v>
       </c>
       <c r="J9">
-        <v>1439</v>
+        <v>0</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -430,7 +430,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">banyok</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -439,25 +439,25 @@
         </is>
       </c>
       <c r="D10">
-        <v>14705</v>
+        <v>5252</v>
       </c>
       <c r="E10">
-        <v>12807</v>
+        <v>5871</v>
       </c>
       <c r="F10">
-        <v>-1897</v>
+        <v>619</v>
       </c>
       <c r="G10">
-        <v>-12.9</v>
+        <v>11.8</v>
       </c>
       <c r="H10">
-        <v>7465</v>
+        <v>2286</v>
       </c>
       <c r="I10">
-        <v>7007</v>
+        <v>2905</v>
       </c>
       <c r="J10">
-        <v>1439</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -466,67 +466,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">slimlux</t>
+          <t xml:space="preserve">fixed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D11">
-        <v>16636</v>
+        <v>4302</v>
       </c>
       <c r="E11">
-        <v>14525</v>
+        <v>4792</v>
       </c>
       <c r="F11">
-        <v>-2111</v>
+        <v>490</v>
       </c>
       <c r="G11">
-        <v>-12.7</v>
+        <v>11.4</v>
       </c>
       <c r="H11">
-        <v>5704</v>
+        <v>3240</v>
       </c>
       <c r="I11">
-        <v>6327</v>
+        <v>3730</v>
       </c>
       <c r="J11">
-        <v>5132</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>2398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">woodjamb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D12">
-        <v>22100</v>
+        <v>18014</v>
       </c>
       <c r="E12">
-        <v>24821</v>
+        <v>15956</v>
       </c>
       <c r="F12">
-        <v>2721</v>
+        <v>-2058</v>
       </c>
       <c r="G12">
-        <v>12.3</v>
+        <v>-11.4</v>
       </c>
       <c r="H12">
-        <v>9023</v>
+        <v>14506</v>
       </c>
       <c r="I12">
-        <v>11745</v>
+        <v>12448</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -538,7 +538,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">banyok</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="D13">
-        <v>5252</v>
+        <v>18301</v>
       </c>
       <c r="E13">
-        <v>5871</v>
+        <v>20135</v>
       </c>
       <c r="F13">
-        <v>619</v>
+        <v>1833</v>
       </c>
       <c r="G13">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>2286</v>
+        <v>10098</v>
       </c>
       <c r="I13">
-        <v>2905</v>
+        <v>11931</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -574,7 +574,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">banyok</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -583,22 +583,22 @@
         </is>
       </c>
       <c r="D14">
-        <v>5252</v>
+        <v>18301</v>
       </c>
       <c r="E14">
-        <v>5871</v>
+        <v>20135</v>
       </c>
       <c r="F14">
-        <v>619</v>
+        <v>1833</v>
       </c>
       <c r="G14">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>2286</v>
+        <v>10098</v>
       </c>
       <c r="I14">
-        <v>2905</v>
+        <v>11931</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -610,7 +610,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">fixed</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -619,58 +619,58 @@
         </is>
       </c>
       <c r="D15">
-        <v>4302</v>
+        <v>15355</v>
       </c>
       <c r="E15">
-        <v>4792</v>
+        <v>13838</v>
       </c>
       <c r="F15">
-        <v>490</v>
+        <v>-1517</v>
       </c>
       <c r="G15">
-        <v>11.4</v>
+        <v>-9.9</v>
       </c>
       <c r="H15">
-        <v>3240</v>
+        <v>7465</v>
       </c>
       <c r="I15">
-        <v>3730</v>
+        <v>7490</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2089</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">woodjamb</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D16">
-        <v>18014</v>
+        <v>19199</v>
       </c>
       <c r="E16">
-        <v>15956</v>
+        <v>21088</v>
       </c>
       <c r="F16">
-        <v>-2058</v>
+        <v>1889</v>
       </c>
       <c r="G16">
-        <v>-11.4</v>
+        <v>9.8</v>
       </c>
       <c r="H16">
-        <v>14506</v>
+        <v>10995</v>
       </c>
       <c r="I16">
-        <v>12448</v>
+        <v>12884</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -682,7 +682,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -691,25 +691,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>18301</v>
+        <v>14705</v>
       </c>
       <c r="E17">
-        <v>20135</v>
+        <v>13291</v>
       </c>
       <c r="F17">
-        <v>1833</v>
+        <v>-1414</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>-9.6</v>
       </c>
       <c r="H17">
-        <v>10098</v>
+        <v>7465</v>
       </c>
       <c r="I17">
-        <v>11931</v>
+        <v>7490</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -718,7 +718,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -727,25 +727,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>18301</v>
+        <v>14705</v>
       </c>
       <c r="E18">
-        <v>20135</v>
+        <v>13301</v>
       </c>
       <c r="F18">
-        <v>1833</v>
+        <v>-1404</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>-9.5</v>
       </c>
       <c r="H18">
-        <v>10098</v>
+        <v>7465</v>
       </c>
       <c r="I18">
-        <v>11931</v>
+        <v>7500</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1439</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -754,37 +754,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">slimlux</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D19">
-        <v>19199</v>
+        <v>16636</v>
       </c>
       <c r="E19">
-        <v>21088</v>
+        <v>15244</v>
       </c>
       <c r="F19">
-        <v>1889</v>
+        <v>-1392</v>
       </c>
       <c r="G19">
-        <v>9.8</v>
+        <v>-8.4</v>
       </c>
       <c r="H19">
-        <v>10995</v>
+        <v>5704</v>
       </c>
       <c r="I19">
-        <v>12884</v>
+        <v>7046</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>5132</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="20">
@@ -1114,31 +1114,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D29">
-        <v>18532</v>
+        <v>22100</v>
       </c>
       <c r="E29">
-        <v>19525</v>
+        <v>23356</v>
       </c>
       <c r="F29">
-        <v>993</v>
+        <v>1257</v>
       </c>
       <c r="G29">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H29">
-        <v>7449</v>
+        <v>9023</v>
       </c>
       <c r="I29">
-        <v>8442</v>
+        <v>10280</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -1150,31 +1150,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D30">
-        <v>18039</v>
+        <v>18532</v>
       </c>
       <c r="E30">
-        <v>17140</v>
+        <v>19525</v>
       </c>
       <c r="F30">
-        <v>-899</v>
+        <v>993</v>
       </c>
       <c r="G30">
-        <v>-5</v>
+        <v>5.4</v>
       </c>
       <c r="H30">
-        <v>15965</v>
+        <v>7449</v>
       </c>
       <c r="I30">
-        <v>15066</v>
+        <v>8442</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -1186,7 +1186,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="D31">
-        <v>10519</v>
+        <v>18039</v>
       </c>
       <c r="E31">
-        <v>10016</v>
+        <v>17140</v>
       </c>
       <c r="F31">
-        <v>-503</v>
+        <v>-899</v>
       </c>
       <c r="G31">
-        <v>-4.8</v>
+        <v>-5</v>
       </c>
       <c r="H31">
-        <v>5133</v>
+        <v>15965</v>
       </c>
       <c r="I31">
-        <v>4630</v>
+        <v>15066</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1227,26 +1227,26 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D32">
-        <v>11060</v>
+        <v>10519</v>
       </c>
       <c r="E32">
-        <v>10539</v>
+        <v>10016</v>
       </c>
       <c r="F32">
-        <v>-521</v>
+        <v>-503</v>
       </c>
       <c r="G32">
-        <v>-4.7</v>
+        <v>-4.8</v>
       </c>
       <c r="H32">
-        <v>5674</v>
+        <v>5133</v>
       </c>
       <c r="I32">
-        <v>5153</v>
+        <v>4630</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -1258,7 +1258,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">folding</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="D33">
-        <v>25189</v>
+        <v>11060</v>
       </c>
       <c r="E33">
-        <v>26357</v>
+        <v>10539</v>
       </c>
       <c r="F33">
-        <v>1169</v>
+        <v>-521</v>
       </c>
       <c r="G33">
-        <v>4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="H33">
-        <v>16985</v>
+        <v>5674</v>
       </c>
       <c r="I33">
-        <v>18154</v>
+        <v>5153</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -1294,31 +1294,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">folding</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D34">
-        <v>16989</v>
+        <v>25189</v>
       </c>
       <c r="E34">
-        <v>17779</v>
+        <v>26357</v>
       </c>
       <c r="F34">
-        <v>790</v>
+        <v>1169</v>
       </c>
       <c r="G34">
         <v>4.6</v>
       </c>
       <c r="H34">
-        <v>5906</v>
+        <v>16985</v>
       </c>
       <c r="I34">
-        <v>6696</v>
+        <v>18154</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1335,26 +1335,26 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D35">
-        <v>16727</v>
+        <v>16989</v>
       </c>
       <c r="E35">
-        <v>17467</v>
+        <v>17779</v>
       </c>
       <c r="F35">
-        <v>739</v>
+        <v>790</v>
       </c>
       <c r="G35">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H35">
-        <v>5644</v>
+        <v>5906</v>
       </c>
       <c r="I35">
-        <v>6383</v>
+        <v>6696</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -1366,31 +1366,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">bar_slide</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D36">
-        <v>18182</v>
+        <v>16727</v>
       </c>
       <c r="E36">
-        <v>18980</v>
+        <v>17467</v>
       </c>
       <c r="F36">
-        <v>798</v>
+        <v>739</v>
       </c>
       <c r="G36">
         <v>4.4</v>
       </c>
       <c r="H36">
-        <v>9959</v>
+        <v>5644</v>
       </c>
       <c r="I36">
-        <v>10757</v>
+        <v>6383</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1402,31 +1402,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">topslide</t>
+          <t xml:space="preserve">bar_slide</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D37">
-        <v>16727</v>
+        <v>18182</v>
       </c>
       <c r="E37">
-        <v>17451</v>
+        <v>18980</v>
       </c>
       <c r="F37">
-        <v>724</v>
+        <v>798</v>
       </c>
       <c r="G37">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H37">
-        <v>5644</v>
+        <v>9959</v>
       </c>
       <c r="I37">
-        <v>6368</v>
+        <v>10757</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1438,31 +1438,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">bansolid</t>
+          <t xml:space="preserve">topslide</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D38">
-        <v>18039</v>
+        <v>16727</v>
       </c>
       <c r="E38">
-        <v>17278</v>
+        <v>17451</v>
       </c>
       <c r="F38">
-        <v>-761</v>
+        <v>724</v>
       </c>
       <c r="G38">
-        <v>-4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H38">
-        <v>15965</v>
+        <v>5644</v>
       </c>
       <c r="I38">
-        <v>15204</v>
+        <v>6368</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1474,31 +1474,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">bar_slide</t>
+          <t xml:space="preserve">bansolid</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D39">
-        <v>14700</v>
+        <v>18039</v>
       </c>
       <c r="E39">
-        <v>15294</v>
+        <v>17278</v>
       </c>
       <c r="F39">
-        <v>594</v>
+        <v>-761</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>-4.2</v>
       </c>
       <c r="H39">
-        <v>6477</v>
+        <v>15965</v>
       </c>
       <c r="I39">
-        <v>7071</v>
+        <v>15204</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D40">
@@ -1551,26 +1551,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D41">
-        <v>15261</v>
+        <v>14700</v>
       </c>
       <c r="E41">
-        <v>15857</v>
+        <v>15294</v>
       </c>
       <c r="F41">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>7038</v>
+        <v>6477</v>
       </c>
       <c r="I41">
-        <v>7634</v>
+        <v>7071</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">bar_slide</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1591,22 +1591,22 @@
         </is>
       </c>
       <c r="D42">
-        <v>21140</v>
+        <v>15261</v>
       </c>
       <c r="E42">
-        <v>20343</v>
+        <v>15857</v>
       </c>
       <c r="F42">
-        <v>-797</v>
+        <v>596</v>
       </c>
       <c r="G42">
-        <v>-3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H42">
-        <v>17375</v>
+        <v>7038</v>
       </c>
       <c r="I42">
-        <v>16578</v>
+        <v>7634</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -1618,31 +1618,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D43">
-        <v>22100</v>
+        <v>21140</v>
       </c>
       <c r="E43">
-        <v>21269</v>
+        <v>20343</v>
       </c>
       <c r="F43">
-        <v>-831</v>
+        <v>-797</v>
       </c>
       <c r="G43">
         <v>-3.8</v>
       </c>
       <c r="H43">
-        <v>9023</v>
+        <v>17375</v>
       </c>
       <c r="I43">
-        <v>8193</v>
+        <v>16578</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -1654,31 +1654,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">fold_euro</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D44">
-        <v>22100</v>
+        <v>20035</v>
       </c>
       <c r="E44">
-        <v>21308</v>
+        <v>19377</v>
       </c>
       <c r="F44">
-        <v>-792</v>
+        <v>-658</v>
       </c>
       <c r="G44">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="H44">
-        <v>9023</v>
+        <v>16270</v>
       </c>
       <c r="I44">
-        <v>8232</v>
+        <v>15612</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D45">
@@ -1731,26 +1731,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D46">
-        <v>20035</v>
+        <v>27485</v>
       </c>
       <c r="E46">
-        <v>19377</v>
+        <v>26572</v>
       </c>
       <c r="F46">
-        <v>-658</v>
+        <v>-913</v>
       </c>
       <c r="G46">
         <v>-3.3</v>
       </c>
       <c r="H46">
-        <v>16270</v>
+        <v>23720</v>
       </c>
       <c r="I46">
-        <v>15612</v>
+        <v>22807</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -1762,31 +1762,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_euro</t>
+          <t xml:space="preserve">pcdoor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D47">
-        <v>27485</v>
+        <v>10519</v>
       </c>
       <c r="E47">
-        <v>26572</v>
+        <v>10186</v>
       </c>
       <c r="F47">
-        <v>-913</v>
+        <v>-333</v>
       </c>
       <c r="G47">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="H47">
-        <v>23720</v>
+        <v>5133</v>
       </c>
       <c r="I47">
-        <v>22807</v>
+        <v>4800</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -1798,7 +1798,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcdoor</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1807,22 +1807,22 @@
         </is>
       </c>
       <c r="D48">
-        <v>10519</v>
+        <v>22100</v>
       </c>
       <c r="E48">
-        <v>10186</v>
+        <v>22800</v>
       </c>
       <c r="F48">
-        <v>-333</v>
+        <v>700</v>
       </c>
       <c r="G48">
-        <v>-3.2</v>
+        <v>3.2</v>
       </c>
       <c r="H48">
-        <v>5133</v>
+        <v>9023</v>
       </c>
       <c r="I48">
-        <v>4800</v>
+        <v>9723</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -1906,31 +1906,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">roof</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D51">
-        <v>34289</v>
+        <v>22100</v>
       </c>
       <c r="E51">
-        <v>33530</v>
+        <v>22747</v>
       </c>
       <c r="F51">
-        <v>-759</v>
+        <v>647</v>
       </c>
       <c r="G51">
-        <v>-2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H51">
-        <v>25458</v>
+        <v>9023</v>
       </c>
       <c r="I51">
-        <v>24700</v>
+        <v>9671</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -1942,31 +1942,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">open_door</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">เทาซาฮาร่า</t>
         </is>
       </c>
       <c r="D52">
-        <v>11130</v>
+        <v>34289</v>
       </c>
       <c r="E52">
-        <v>10911</v>
+        <v>33530</v>
       </c>
       <c r="F52">
-        <v>-219</v>
+        <v>-759</v>
       </c>
       <c r="G52">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="H52">
-        <v>8293</v>
+        <v>25458</v>
       </c>
       <c r="I52">
-        <v>8074</v>
+        <v>24700</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -1978,31 +1978,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">euro_slide</t>
+          <t xml:space="preserve">open_door</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">อบขาว</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D53">
-        <v>32720</v>
+        <v>11130</v>
       </c>
       <c r="E53">
-        <v>32112</v>
+        <v>10911</v>
       </c>
       <c r="F53">
-        <v>-608</v>
+        <v>-219</v>
       </c>
       <c r="G53">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="H53">
-        <v>23889</v>
+        <v>8293</v>
       </c>
       <c r="I53">
-        <v>23281</v>
+        <v>8074</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ดำ</t>
+          <t xml:space="preserve">อบขาว</t>
         </is>
       </c>
       <c r="D54">
@@ -2050,31 +2050,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">pivot</t>
+          <t xml:space="preserve">euro_slide</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ลายไม้สักทอง</t>
+          <t xml:space="preserve">ดำ</t>
         </is>
       </c>
       <c r="D55">
-        <v>15582</v>
+        <v>32720</v>
       </c>
       <c r="E55">
-        <v>15320</v>
+        <v>32112</v>
       </c>
       <c r="F55">
-        <v>-262</v>
+        <v>-608</v>
       </c>
       <c r="G55">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="H55">
-        <v>12580</v>
+        <v>23889</v>
       </c>
       <c r="I55">
-        <v>12318</v>
+        <v>23281</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -2086,31 +2086,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate</t>
+          <t xml:space="preserve">pivot</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">เทาซาฮาร่า</t>
+          <t xml:space="preserve">ลายไม้สักทอง</t>
         </is>
       </c>
       <c r="D56">
-        <v>25438</v>
+        <v>15582</v>
       </c>
       <c r="E56">
-        <v>25836</v>
+        <v>15320</v>
       </c>
       <c r="F56">
-        <v>398</v>
+        <v>-262</v>
       </c>
       <c r="G56">
-        <v>1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="H56">
-        <v>13860</v>
+        <v>12580</v>
       </c>
       <c r="I56">
-        <v>14258</v>
+        <v>12318</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -2122,7 +2122,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">fold_lift</t>
+          <t xml:space="preserve">gate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2131,22 +2131,22 @@
         </is>
       </c>
       <c r="D57">
-        <v>14760</v>
+        <v>25438</v>
       </c>
       <c r="E57">
-        <v>14540</v>
+        <v>25836</v>
       </c>
       <c r="F57">
-        <v>-220</v>
+        <v>398</v>
       </c>
       <c r="G57">
-        <v>-1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H57">
-        <v>12520</v>
+        <v>13860</v>
       </c>
       <c r="I57">
-        <v>12300</v>
+        <v>14258</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -2158,7 +2158,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">roof</t>
+          <t xml:space="preserve">fold_lift</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2167,22 +2167,22 @@
         </is>
       </c>
       <c r="D58">
-        <v>22100</v>
+        <v>14760</v>
       </c>
       <c r="E58">
-        <v>21783</v>
+        <v>14540</v>
       </c>
       <c r="F58">
-        <v>-317</v>
+        <v>-220</v>
       </c>
       <c r="G58">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="H58">
-        <v>9023</v>
+        <v>12520</v>
       </c>
       <c r="I58">
-        <v>8707</v>
+        <v>12300</v>
       </c>
       <c r="J58">
         <v>0</v>
